--- a/data/trans_dic/AIRE_1_R-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/AIRE_1_R-Provincia-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que no está dispuesta a pagar para reducir la contaminación del aire (impuesto durante 5 años)</t>
+          <t>Población que no está dispuesta a pagar para reducir la contaminación del aire (impuesto durante 5 años) (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>69,73; 87,16</t>
+          <t>69,81; 86,76</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>79,05; 88,93</t>
+          <t>79,75; 88,75</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>77,33; 86,95</t>
+          <t>76,87; 86,9</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>64,26; 79,56</t>
+          <t>64,75; 79,44</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>72,41; 82,87</t>
+          <t>72,35; 82,61</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>70,16; 79,66</t>
+          <t>70,13; 79,45</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>66,02; 79,66</t>
+          <t>65,83; 79,63</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>68,08; 80,17</t>
+          <t>68,01; 79,57</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>69,22; 78,18</t>
+          <t>69,16; 78,18</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>59,62; 77,24</t>
+          <t>59,73; 78,14</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>34,24; 75,61</t>
+          <t>38,91; 75,81</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>48,56; 73,52</t>
+          <t>46,69; 73,75</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>36,09; 53,42</t>
+          <t>36,17; 51,68</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>45,7; 58,01</t>
+          <t>45,9; 57,19</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>43,66; 53,3</t>
+          <t>43,63; 53,42</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>70,59; 83,64</t>
+          <t>70,03; 83,29</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>73,33; 84,83</t>
+          <t>73,37; 85,02</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>73,99; 82,89</t>
+          <t>74,22; 82,99</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>64,09; 76,55</t>
+          <t>65,1; 77,59</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>66,4; 93,21</t>
+          <t>66,32; 93,43</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>67,8; 88,92</t>
+          <t>68,27; 89,0</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>78,43; 86,3</t>
+          <t>78,44; 86,38</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>87,37; 92,47</t>
+          <t>87,24; 92,77</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>83,85; 88,53</t>
+          <t>84,04; 88,67</t>
         </is>
       </c>
     </row>
@@ -972,17 +972,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>70,89; 76,0</t>
+          <t>70,85; 75,95</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>73,6; 84,43</t>
+          <t>73,65; 84,14</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>73,35; 80,19</t>
+          <t>73,41; 80,12</t>
         </is>
       </c>
     </row>
@@ -1029,7 +1029,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que no está dispuesta a pagar para reducir la contaminación del aire (impuesto durante 5 años)</t>
+          <t>Población que no está dispuesta a pagar para reducir la contaminación del aire (impuesto durante 5 años) (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1134,17 +1134,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>109602; 136999</t>
+          <t>109726; 136360</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>129095; 145234</t>
+          <t>130243; 144941</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>247837; 278663</t>
+          <t>246357; 278515</t>
         </is>
       </c>
     </row>
@@ -1207,17 +1207,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>175003; 216669</t>
+          <t>176345; 216343</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>169442; 193913</t>
+          <t>169291; 193292</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>355226; 403368</t>
+          <t>355082; 402299</t>
         </is>
       </c>
     </row>
@@ -1280,17 +1280,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>123333; 148812</t>
+          <t>122975; 148753</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>123504; 145442</t>
+          <t>123378; 144351</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>254872; 287861</t>
+          <t>254651; 287858</t>
         </is>
       </c>
     </row>
@@ -1353,17 +1353,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>102051; 132226</t>
+          <t>102253; 133759</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>78469; 173256</t>
+          <t>89160; 173722</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>194413; 294341</t>
+          <t>186921; 295240</t>
         </is>
       </c>
     </row>
@@ -1426,17 +1426,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>37094; 54903</t>
+          <t>37177; 53109</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>58778; 74613</t>
+          <t>59032; 73558</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>101025; 123329</t>
+          <t>100949; 123606</t>
         </is>
       </c>
     </row>
@@ -1499,17 +1499,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>99680; 118114</t>
+          <t>98886; 117618</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>102946; 119091</t>
+          <t>102997; 119357</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>208359; 233400</t>
+          <t>209010; 233707</t>
         </is>
       </c>
     </row>
@@ -1572,17 +1572,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>179994; 214973</t>
+          <t>182831; 217889</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>330040; 463327</t>
+          <t>329655; 464391</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>527399; 691676</t>
+          <t>531050; 692296</t>
         </is>
       </c>
     </row>
@@ -1645,17 +1645,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>268789; 295765</t>
+          <t>268836; 296048</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>291700; 308710</t>
+          <t>291249; 309707</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>567291; 598969</t>
+          <t>568594; 599940</t>
         </is>
       </c>
     </row>
@@ -1718,17 +1718,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>1173195; 1257849</t>
+          <t>1172583; 1257039</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>1404113; 1610666</t>
+          <t>1405072; 1605310</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>2613514; 2857112</t>
+          <t>2615583; 2854479</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/AIRE_1_R-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/AIRE_1_R-Provincia-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>80,5%</t>
+          <t>83,1%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>84,83%</t>
+          <t>85,24%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>82,71%</t>
+          <t>84,21%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>69,81; 86,76</t>
+          <t>76,2; 87,94</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>79,75; 88,75</t>
+          <t>80,68; 88,84</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>76,87; 86,9</t>
+          <t>80,47; 87,87</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>72,65%</t>
+          <t>72,67%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>78,21%</t>
+          <t>78,54%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>75,22%</t>
+          <t>75,46%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>64,75; 79,44</t>
+          <t>64,07; 79,52</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>72,35; 82,61</t>
+          <t>72,85; 82,92</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>70,13; 79,45</t>
+          <t>70,93; 79,72</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>73,44%</t>
+          <t>74,51%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>74,4%</t>
+          <t>75,14%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>73,91%</t>
+          <t>74,82%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>65,83; 79,63</t>
+          <t>67,54; 80,45</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>68,01; 79,57</t>
+          <t>68,79; 80,34</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>69,16; 78,18</t>
+          <t>70,01; 79,14</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>69,34%</t>
+          <t>69,92%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>63,24%</t>
+          <t>74,83%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>65,85%</t>
+          <t>72,5%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>59,73; 78,14</t>
+          <t>60,51; 77,29</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>38,91; 75,81</t>
+          <t>68,58; 80,03</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>46,69; 73,75</t>
+          <t>66,76; 77,08</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>43,73%</t>
+          <t>44,42%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>51,59%</t>
+          <t>51,56%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>48,1%</t>
+          <t>48,35%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>36,17; 51,68</t>
+          <t>36,72; 52,96</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>45,9; 57,19</t>
+          <t>45,81; 57,44</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>43,63; 53,42</t>
+          <t>43,67; 53,36</t>
         </is>
       </c>
     </row>
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>77,44%</t>
+          <t>78,08%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>80,23%</t>
+          <t>80,41%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>78,83%</t>
+          <t>79,26%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>70,03; 83,29</t>
+          <t>70,6; 83,51</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>73,37; 85,02</t>
+          <t>73,9; 85,6</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>74,22; 82,99</t>
+          <t>74,8; 83,2</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>71,01%</t>
+          <t>68,69%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>81,27%</t>
+          <t>67,42%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>77,56%</t>
+          <t>68,02%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>65,1; 77,59</t>
+          <t>62,68; 74,32</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>66,32; 93,43</t>
+          <t>62,62; 71,75</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>68,27; 89,0</t>
+          <t>64,05; 71,4</t>
         </is>
       </c>
     </row>
@@ -899,17 +899,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>82,86%</t>
+          <t>83,77%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>90,06%</t>
+          <t>90,24%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>86,41%</t>
+          <t>86,94%</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>78,44; 86,38</t>
+          <t>79,96; 86,98</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>87,24; 92,77</t>
+          <t>87,49; 92,75</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>84,04; 88,67</t>
+          <t>84,66; 89,12</t>
         </is>
       </c>
     </row>
@@ -949,17 +949,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>73,59%</t>
+          <t>73,91%</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>77,84%</t>
+          <t>76,82%</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>75,87%</t>
+          <t>75,39%</t>
         </is>
       </c>
     </row>
@@ -972,17 +972,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>70,85; 75,95</t>
+          <t>71,31; 76,06</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>73,65; 84,14</t>
+          <t>74,97; 78,56</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>73,41; 80,12</t>
+          <t>73,95; 76,8</t>
         </is>
       </c>
     </row>
@@ -1111,17 +1111,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>126529</t>
+          <t>136743</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>138536</t>
+          <t>151180</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>265065</t>
+          <t>287923</t>
         </is>
       </c>
     </row>
@@ -1134,17 +1134,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>109726; 136360</t>
+          <t>125395; 144710</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>130243; 144941</t>
+          <t>143093; 157559</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>246357; 278515</t>
+          <t>275135; 300432</t>
         </is>
       </c>
     </row>
@@ -1184,17 +1184,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>197856</t>
+          <t>198346</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>183008</t>
+          <t>193887</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>380864</t>
+          <t>392233</t>
         </is>
       </c>
     </row>
@@ -1207,17 +1207,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>176345; 216343</t>
+          <t>174877; 217040</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>169291; 193292</t>
+          <t>179855; 204714</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>355082; 402299</t>
+          <t>368719; 414404</t>
         </is>
       </c>
     </row>
@@ -1257,17 +1257,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>137186</t>
+          <t>141529</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>134963</t>
+          <t>140595</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>272150</t>
+          <t>282125</t>
         </is>
       </c>
     </row>
@@ -1280,17 +1280,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>122975; 148753</t>
+          <t>128286; 152813</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>123378; 144351</t>
+          <t>128713; 150308</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>254651; 287858</t>
+          <t>263989; 298403</t>
         </is>
       </c>
     </row>
@@ -1330,17 +1330,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>118697</t>
+          <t>138911</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>144923</t>
+          <t>164976</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>263620</t>
+          <t>303887</t>
         </is>
       </c>
     </row>
@@ -1353,17 +1353,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>102253; 133759</t>
+          <t>120228; 153569</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>89160; 173722</t>
+          <t>151183; 176419</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>186921; 295240</t>
+          <t>279803; 323052</t>
         </is>
       </c>
     </row>
@@ -1403,17 +1403,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>44942</t>
+          <t>50304</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>66354</t>
+          <t>71458</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>111296</t>
+          <t>121763</t>
         </is>
       </c>
     </row>
@@ -1426,17 +1426,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>37177; 53109</t>
+          <t>41580; 59975</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>59032; 73558</t>
+          <t>63488; 79598</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>100949; 123606</t>
+          <t>109975; 134367</t>
         </is>
       </c>
     </row>
@@ -1476,17 +1476,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>109355</t>
+          <t>109283</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>112622</t>
+          <t>115202</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>221978</t>
+          <t>224485</t>
         </is>
       </c>
     </row>
@@ -1499,17 +1499,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>98886; 117618</t>
+          <t>98812; 116890</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>102997; 119357</t>
+          <t>105881; 122647</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>209010; 233707</t>
+          <t>211857; 235653</t>
         </is>
       </c>
     </row>
@@ -1549,17 +1549,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>199410</t>
+          <t>220879</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>403939</t>
+          <t>240713</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>603350</t>
+          <t>461593</t>
         </is>
       </c>
     </row>
@@ -1572,17 +1572,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>182831; 217889</t>
+          <t>201535; 238969</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>329655; 464391</t>
+          <t>223575; 256157</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>531050; 692296</t>
+          <t>434612; 484466</t>
         </is>
       </c>
     </row>
@@ -1622,17 +1622,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>283970</t>
+          <t>335232</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>300655</t>
+          <t>348152</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>584626</t>
+          <t>683384</t>
         </is>
       </c>
     </row>
@@ -1645,17 +1645,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>268836; 296048</t>
+          <t>319979; 348095</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>291249; 309707</t>
+          <t>337567; 357861</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>568594; 599940</t>
+          <t>665458; 700488</t>
         </is>
       </c>
     </row>
@@ -1695,17 +1695,17 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>1217946</t>
+          <t>1331230</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>1485002</t>
+          <t>1426164</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2702949</t>
+          <t>2757393</t>
         </is>
       </c>
     </row>
@@ -1718,17 +1718,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>1172583; 1257039</t>
+          <t>1284265; 1369981</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>1405072; 1605310</t>
+          <t>1391742; 1458383</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>2615583; 2854479</t>
+          <t>2704879; 2809037</t>
         </is>
       </c>
     </row>
